--- a/MMORPG_SERVER/Data/Excel/TalkDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/TalkDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8EDC95-B321-46E3-8649-26C5D69854FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5A003C-C074-4369-B95A-0A027CFE8DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,6 +74,19 @@
   ["毒蝎龙就在黑森林入口往南走2里地的乱石堆附近，它们的硬壳怕锋利的武器，你可得小心些"],
   ["这把初级宝剑趁手得很，你一定会喜欢，打完怪物即可获得，加油！"]
 ]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>媒婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["哎哟小英雄！可算盼着你回来了！刚听说你把那些怪物收拾得服服帖帖，真是了不起哟！”],
+["不过闯荡江湖哪能没个伴儿？你得去好友系统中好好搭个话结个好友"],
+["往后打怪做任务也能互相帮衬，这事儿办完直接得 500 金币奖励呢！"],
+["还有啊，公会可是咱们的靠山！要么加入其他人的公会，要么自己建一个，还能再拿 500 金币，多划算！"]
+["这俩事儿可不耽误，结交好友有人配合，入了公会有大家伙儿撑腰，关键是每桩都有 500 金币拿！早办早得好处呀！"]
+["你想想，好友、公会齐活了，打怪升级顺风顺水，还能白得 1000 金币，这等好事可别错过！快去行动吧！"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -405,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.875" style="1" customWidth="1"/>
@@ -457,6 +470,17 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:3" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
